--- a/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-32,34; 5,4</t>
+          <t>-31,58; 5,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,36; 27,71</t>
+          <t>-5,46; 27,15</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-26,79; 12,05</t>
+          <t>-24,21; 12,96</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-12,26; 34,77</t>
+          <t>-11,79; 36,72</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-63,87; 17,03</t>
+          <t>-66,8; 17,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-10,4; 91,12</t>
+          <t>-11,91; 90,65</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-56,0; 44,31</t>
+          <t>-51,36; 44,88</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,95; 110,44</t>
+          <t>-21,52; 121,25</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-30,19; 1,39</t>
+          <t>-29,99; 3,19</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-20,38; 5,55</t>
+          <t>-19,01; 7,39</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,33; 22,48</t>
+          <t>-9,18; 20,94</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-19,14; 17,05</t>
+          <t>-18,5; 16,08</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-55,59; 3,31</t>
+          <t>-54,93; 10,35</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-47,35; 16,43</t>
+          <t>-43,72; 23,87</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,28; 84,74</t>
+          <t>-20,64; 80,46</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-34,15; 42,57</t>
+          <t>-32,8; 38,44</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,35; 18,9</t>
+          <t>-26,34; 17,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-17,65; 22,7</t>
+          <t>-15,21; 23,98</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,91; 5,59</t>
+          <t>-26,46; 8,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 36,37</t>
+          <t>-4,48; 34,69</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-61,38; 84,37</t>
+          <t>-59,29; 76,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-34,5; 78,26</t>
+          <t>-32,1; 86,08</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,78; 18,08</t>
+          <t>-55,76; 25,06</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 109,63</t>
+          <t>-7,62; 105,09</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-18,71; 19,77</t>
+          <t>-17,59; 19,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-10,25; 27,81</t>
+          <t>-11,89; 27,08</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,25; 37,55</t>
+          <t>-3,4; 36,91</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,3; 2,83</t>
+          <t>-42,7; 2,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-43,43; 66,31</t>
+          <t>-37,74; 67,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-21,79; 94,53</t>
+          <t>-24,16; 93,0</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,33; 174,73</t>
+          <t>-8,26; 169,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,43; 3,46</t>
+          <t>-82,33; 3,61</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,03; 1,06</t>
+          <t>-18,63; 0,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 11,5</t>
+          <t>-5,55; 11,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,67; 11,02</t>
+          <t>-7,22; 11,68</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,03; 7,81</t>
+          <t>-21,18; 8,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,72; 3,0</t>
+          <t>-40,44; 1,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,09; 33,54</t>
+          <t>-13,26; 32,22</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 34,85</t>
+          <t>-17,78; 36,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 18,62</t>
+          <t>-44,96; 21,0</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 5,44</t>
+          <t>-31,96; 5,7</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,46; 27,15</t>
+          <t>-4,31; 28,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-24,21; 12,96</t>
+          <t>-27,51; 10,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-11,79; 36,72</t>
+          <t>-13,08; 33,74</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-66,8; 17,41</t>
+          <t>-65,95; 20,71</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,91; 90,65</t>
+          <t>-8,9; 95,49</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-51,36; 44,88</t>
+          <t>-55,46; 41,07</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-21,52; 121,25</t>
+          <t>-26,38; 100,81</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-29,99; 3,19</t>
+          <t>-28,67; 2,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,01; 7,39</t>
+          <t>-19,44; 5,82</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-9,18; 20,94</t>
+          <t>-8,81; 21,36</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,5; 16,08</t>
+          <t>-18,08; 17,4</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,93; 10,35</t>
+          <t>-54,96; 8,0</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-43,72; 23,87</t>
+          <t>-46,48; 18,68</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-20,64; 80,46</t>
+          <t>-21,76; 81,89</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,8; 38,44</t>
+          <t>-32,78; 46,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-26,34; 17,9</t>
+          <t>-27,89; 15,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,21; 23,98</t>
+          <t>-15,71; 21,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,46; 8,04</t>
+          <t>-26,03; 8,1</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 34,69</t>
+          <t>-2,05; 35,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-59,29; 76,35</t>
+          <t>-64,18; 65,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,1; 86,08</t>
+          <t>-32,5; 74,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-55,76; 25,06</t>
+          <t>-56,01; 32,8</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-7,62; 105,09</t>
+          <t>-4,6; 106,55</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-17,59; 19,87</t>
+          <t>-16,12; 20,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 27,08</t>
+          <t>-11,89; 26,47</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 36,91</t>
+          <t>-3,63; 37,25</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-42,7; 2,06</t>
+          <t>-41,6; 1,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-37,74; 67,23</t>
+          <t>-35,96; 68,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,16; 93,0</t>
+          <t>-24,22; 80,93</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 169,78</t>
+          <t>-8,69; 175,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-82,33; 3,61</t>
+          <t>-79,31; 3,94</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-18,63; 0,56</t>
+          <t>-17,37; 1,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,55; 11,33</t>
+          <t>-5,23; 12,13</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,22; 11,68</t>
+          <t>-6,86; 11,7</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-21,18; 8,71</t>
+          <t>-23,15; 7,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-40,44; 1,45</t>
+          <t>-38,08; 3,03</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,26; 32,22</t>
+          <t>-12,14; 33,94</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-17,78; 36,04</t>
+          <t>-16,31; 37,0</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-44,96; 21,0</t>
+          <t>-47,8; 18,84</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos para  el dolor y/o para bajar la fiebre</t>
+          <t>Menores que consumieron medicamentos para  el dolor y/o para bajar la fiebre</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,79</t>
+          <t>11,49</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>24,96%</t>
+          <t>26,64%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-31,96; 5,7</t>
+          <t>-32,34; 5,4</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-4,31; 28,24</t>
+          <t>-4,36; 27,71</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-27,51; 10,66</t>
+          <t>-26,79; 12,05</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-13,08; 33,74</t>
+          <t>-11,38; 35,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 20,71</t>
+          <t>-63,87; 17,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-8,9; 95,49</t>
+          <t>-10,4; 91,12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-55,46; 41,07</t>
+          <t>-56,0; 44,31</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,38; 100,81</t>
+          <t>-23,78; 107,71</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-0,91</t>
+          <t>-0,99</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-1,93%</t>
+          <t>-2,04%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-28,67; 2,95</t>
+          <t>-30,19; 1,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-19,44; 5,82</t>
+          <t>-20,38; 5,55</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 21,36</t>
+          <t>-8,33; 22,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-18,08; 17,4</t>
+          <t>-18,79; 15,97</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-54,96; 8,0</t>
+          <t>-55,59; 3,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-46,48; 18,68</t>
+          <t>-47,35; 16,43</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-21,76; 81,89</t>
+          <t>-20,28; 84,74</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-32,78; 46,25</t>
+          <t>-33,28; 40,59</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>17,86</t>
+          <t>18,72</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>43,03%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-27,89; 15,53</t>
+          <t>-27,35; 18,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-15,71; 21,56</t>
+          <t>-17,65; 22,7</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-26,03; 8,1</t>
+          <t>-26,91; 5,59</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 35,16</t>
+          <t>-1,44; 37,07</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-64,18; 65,59</t>
+          <t>-61,38; 84,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-32,5; 74,91</t>
+          <t>-34,5; 78,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-56,01; 32,8</t>
+          <t>-55,78; 18,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 106,55</t>
+          <t>-0,87; 113,24</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-18,31</t>
+          <t>-3,82</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-43,71%</t>
+          <t>-9,19%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-16,12; 20,83</t>
+          <t>-18,71; 19,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 26,47</t>
+          <t>-10,25; 27,81</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 37,25</t>
+          <t>-4,25; 37,55</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-41,6; 1,29</t>
+          <t>-20,84; 14,35</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-35,96; 68,16</t>
+          <t>-43,43; 66,31</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,22; 80,93</t>
+          <t>-21,79; 94,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-8,69; 175,15</t>
+          <t>-10,33; 174,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-79,31; 3,94</t>
+          <t>-42,77; 42,53</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,72</t>
+          <t>4,73</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-8,46%</t>
+          <t>10,75%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-17,37; 1,13</t>
+          <t>-18,03; 1,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 12,13</t>
+          <t>-5,29; 11,5</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 11,7</t>
+          <t>-6,67; 11,02</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-23,15; 7,93</t>
+          <t>-4,44; 14,82</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-38,08; 3,03</t>
+          <t>-38,72; 3,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 33,94</t>
+          <t>-12,09; 33,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-16,31; 37,0</t>
+          <t>-16,06; 34,85</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 18,84</t>
+          <t>-8,95; 37,57</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP16A02-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>-13,15</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>11,43</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-7,25</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>11,49</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>-32,43%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>29,45%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>-18,4%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>26,64%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>-2.413017622232223</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>3.453738641556421</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>0.3984704122432854</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-0.02092115508796344</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.2436182648422992</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>0.7459130025237274</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.09951168231539066</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.001405544645945148</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-32,34; 5,4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-4,36; 27,71</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-26,79; 12,05</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-11,38; 35,49</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-63,87; 17,03</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-10,4; 91,12</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-56,0; 44,31</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-23,78; 107,71</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-8.111959948442893</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-1.488377405808974</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-3.494609897927515</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-9.083207328976235</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.6494368527877648</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.2870087840667468</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6186074559456461</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.4788184334455318</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>3.398419831326972</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>7.918563501910531</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>3.985371495235027</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>9.875519928038718</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5000940349986159</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>2.743439967345943</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>1.824511540823555</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>1.022835772627551</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-12,96</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-7,03</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,41</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-0,99</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-28,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-18,7%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>21,38%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-2,04%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-30,19; 1,39</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-20,38; 5,55</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-8,33; 22,48</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-18,79; 15,97</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-55,59; 3,31</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-47,35; 16,43</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-20,28; 84,74</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-33,28; 40,59</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.599917685250799</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-3.668714633215047</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>1.441326041999939</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>0.6056754280249654</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.3893639530845867</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.5081960779462051</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.3061204811470618</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.04752350509805513</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-5,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-9,71</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>18,72</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-16,26%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,08%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-25,06%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>43,03%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-7.182795073523307</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-6.996758020942472</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-1.881707846164621</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-5.672375711792498</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6395518861277845</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.7652732012396817</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.3160206688948948</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.3421758562993499</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-27,35; 18,9</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-17,65; 22,7</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-26,91; 5,59</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 37,07</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-61,38; 84,37</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-34,5; 78,26</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-55,78; 18,08</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-0,87; 113,24</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>0.02388832501533716</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>-0.01007548772690259</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>4.749478468419905</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>7.18051849315176</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.01431264359216598</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.02652683148902547</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>1.404038210685354</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.7368955835618719</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>1,44</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>8,51</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>16,97</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-3,82</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>21,11%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>49,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-9,19%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-0.7429011260494389</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.02452743233879867</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-0.9061627204443867</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>4.027747078538433</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.1238484515038297</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.00435464898729778</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.2360432127217643</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>0.4212666186195827</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-18,71; 19,77</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-10,25; 27,81</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-4,25; 37,55</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-20,84; 14,35</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-43,43; 66,31</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-21,79; 94,53</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-10,33; 174,73</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-42,77; 42,53</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-5.198322318616353</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-4.624427856592899</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-4.17078091683527</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-1.679485927106447</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.6741253111921323</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5713657969537237</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.7737774120703429</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.156111580055541</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>3.708631433295975</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>3.871180902355522</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>2.143097901430269</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>9.821506916833457</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>1.15976904038616</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.167255041621272</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>1.059006121339779</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>1.406442213664995</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-1.100608851276627</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>2.323983186222434</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3298989333869986</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.496432650867829</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1475426177542876</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.7666129362315823</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.1154899026762461</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.1691569299234388</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-5.046413153925557</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-1.080475484202113</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-3.266791047737081</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-5.695788896893358</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5237439337834214</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2746843272380975</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7481330521961842</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.5097355708634368</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.722257032145502</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>5.787457922785355</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>2.641977244711661</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.639996957966117</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.5519787950429939</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>4.069671509681983</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>2.320648491633567</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.4303942652517652</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-8,28</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>2,93</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,95</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>4,73</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-20,08%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>7,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>5,31%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>10,75%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-18,03; 1,06</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-5,29; 11,5</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,67; 11,02</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-4,44; 14,82</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-38,72; 3,0</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-12,09; 33,54</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-16,06; 34,85</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-8,95; 37,57</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-2.147550396462416</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>0.0026693380173963</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>0.1309507165159936</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.7304544966082599</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.2615357865625642</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>0.0004957879606828764</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.03325226120339658</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.07050705099158684</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-4.367374475053996</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-1.913559872394029</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.519951932790151</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-2.24043303881145</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.4574221769685463</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.3068954220078444</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.3174816945821887</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1881747554229367</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>0.04272646517852274</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>2.157082612305553</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>1.701109120780015</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.439527584093203</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.008211232221986156</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.4987000980050025</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.5375322164996861</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.3974714982335945</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
